--- a/samples/ss_tjati_ungaran3_ingest.xlsx
+++ b/samples/ss_tjati_ungaran3_ingest.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/samples/ss_tjati_ungaran3_ingest.xlsx
+++ b/samples/ss_tjati_ungaran3_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2 Tanjungjati 500/150 kV</t>
+          <t>IBT 1 Tanjungjati 500/150 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -828,14 +828,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -866,31 +862,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jelok</t>
+          <t>IBT 2 Tanjungjati 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JELOK</t>
+          <t>IBT 2 TJATI7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TJATI7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TJATI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -907,7 +917,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1;2</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -923,17 +933,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLTA Jelok</t>
+          <t>Jelok</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_JELOK</t>
+          <t>JELOK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -959,10 +969,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -976,12 +990,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLTA Timo</t>
+          <t>PLTA Jelok</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KIT_TIMO</t>
+          <t>KIT_JELOK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1029,17 +1043,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ungaran (bus 150 kV)</t>
+          <t>PLTA Timo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNGAR</t>
+          <t>KIT_TIMO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1065,14 +1079,10 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1086,12 +1096,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tambaklorok</t>
+          <t>Ungaran (bus 150 kV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TBROK</t>
+          <t>UNGAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1122,10 +1132,14 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1139,17 +1153,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PLTGU Tambaklorok Blok B2</t>
+          <t>Tambaklorok</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KIT_TBROKB2</t>
+          <t>TBROK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1192,12 +1206,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLTGU Tambaklorok Blok B1</t>
+          <t>PLTGU Tambaklorok Blok B2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KIT_TBROKB1</t>
+          <t>KIT_TBROKB2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1245,17 +1259,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tanjungjati (bus 150 kV)</t>
+          <t>PLTGU Tambaklorok Blok B1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>KIT_TBROKB1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1298,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rembang KIT</t>
+          <t>Tanjungjati (bus 150 kV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RBKIT</t>
+          <t>TJATI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1334,14 +1348,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1355,17 +1365,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PLTU Rembang</t>
+          <t>Rembang KIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT_RBANG</t>
+          <t>RBKIT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1391,10 +1401,14 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1408,21 +1422,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bawen</t>
+          <t>PLTU Rembang</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAWEN</t>
+          <t>KIT_RBANG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1461,12 +1475,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mranggen</t>
+          <t>Bawen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MRGEN</t>
+          <t>BAWEN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1514,12 +1528,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sayung</t>
+          <t>Mranggen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SYUNG</t>
+          <t>MRGEN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1567,12 +1581,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jepara</t>
+          <t>Sayung</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JPARA</t>
+          <t>SYUNG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1620,12 +1634,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pati</t>
+          <t>Jepara</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PATI</t>
+          <t>JPARA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1656,14 +1670,10 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1677,12 +1687,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rembang</t>
+          <t>Pati</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RBANG</t>
+          <t>PATI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1713,10 +1723,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1730,12 +1744,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sugihrahayu</t>
+          <t>Rembang</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SGRAH</t>
+          <t>RBANG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1744,7 +1758,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1766,14 +1780,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1787,12 +1797,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Secang (Bus 1)</t>
+          <t>Sugihrahayu</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SCANG</t>
+          <t>SGRAH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1813,11 +1823,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Bus 1</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
@@ -1827,10 +1833,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1844,12 +1854,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sambungan</t>
+          <t>Secang (Bus 1)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SBGAN</t>
+          <t>SCANG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1872,7 +1882,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>KTT SBGAN</t>
+          <t>Bus 1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1901,12 +1911,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kudus</t>
+          <t>Sambungan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KUDUS</t>
+          <t>SBGAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1927,7 +1937,11 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>KTT SBGAN</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -1937,14 +1951,10 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1958,12 +1968,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jekulo</t>
+          <t>Kudus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JKULO</t>
+          <t>KUDUS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1994,10 +2004,14 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2011,12 +2025,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sindo</t>
+          <t>Jekulo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SINDO</t>
+          <t>JKULO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2037,11 +2051,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>KTT SINDO</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
@@ -2068,12 +2078,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mandari</t>
+          <t>Sindo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDARI</t>
+          <t>SINDO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2082,7 +2092,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2094,7 +2104,11 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>KTT SINDO</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -2104,14 +2118,10 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2125,12 +2135,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Purwodadi</t>
+          <t>Mandari</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PRWDI</t>
+          <t>MDARI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2161,10 +2171,14 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2178,12 +2192,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blora</t>
+          <t>Purwodadi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BLORA</t>
+          <t>PRWDI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2214,14 +2228,10 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2235,12 +2245,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kanetug</t>
+          <t>Blora</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KNTUG</t>
+          <t>BLORA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2249,7 +2259,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2276,7 +2286,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2292,12 +2302,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kedungombo</t>
+          <t>Kanetug</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KDNBO</t>
+          <t>KNTUG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2328,10 +2338,14 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2345,17 +2359,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PLTA Kedungombo</t>
+          <t>Kedungombo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KIT_KDNBO</t>
+          <t>KDNBO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2398,17 +2412,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cepu</t>
+          <t>PLTA Kedungombo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CEPU</t>
+          <t>KIT_KDNBO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2434,14 +2448,10 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2455,12 +2465,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gajahan</t>
+          <t>Cepu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GJYAN</t>
+          <t>CEPU</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2469,7 +2479,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2496,7 +2506,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2512,12 +2522,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boyolali (SS Boyolali)</t>
+          <t>Gajahan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>GJYAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2526,7 +2536,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2538,28 +2548,24 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Boyolali 1,2</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2573,12 +2579,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Temanggung (SS Kesugihan)</t>
+          <t>Boyolali (SS Boyolali)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TMGNG</t>
+          <t>BYOLI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2587,7 +2593,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2601,7 +2607,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Kesugihan 1,2</t>
+          <t>batas ke Subsistem Boyolali 1,2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2634,12 +2640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bojonegoro (UP2B Jatim)</t>
+          <t>Temanggung (SS Kesugihan)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BJGRO</t>
+          <t>TMGNG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2648,7 +2654,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2662,7 +2668,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>batas ke UP2B Jawa Timur (SS Ngimbang)</t>
+          <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -2688,6 +2694,67 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bojonegoro (UP2B Jatim)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BJGRO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>batas ke UP2B Jawa Timur (SS Ngimbang)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4854,12 +4921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] IBT-3 Ungaran akan mengalami overload apabila terjadi kontingensi N-1-1 pada IBT Tanjungjati 1,2</t>
+          <t>[N-1-1] IBT-3 Ungaran akan mengalami overload apabila terjadi kontingensi N-1-1 pada IBT Tanjungjati 1,2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4889,12 +4956,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] IBT-3 Ungaran yang memasok Subsistem Tanjung Jati mayoritas konsumen industri (MVAR-nya besar) untuk pasokan wilayah Magelang &amp; Kudus sehingga berpotensi drop tegangan</t>
+          <t>[BELUM_DITETAPKAN] IBT-3 Ungaran yang memasok Subsistem Tanjung Jati mayoritas konsumen industri (MVAR-nya besar) untuk pasokan wilayah Magelang &amp; Kudus sehingga berpotensi drop tegangan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4924,12 +4991,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] 1. Outlet PLTU Rembang 2x280 MW terhubung dengan Subsistem Tanjung Jati melalui 2 sirkit radial SUTT 150 kV PLTU Rembang-Pati- Jekulo-Kudus dan PLTU Rembang-Sindo-Blora- Cepu. 2. Outlet PLTU Rembang terletak pada tower combined pada T.3-T.70 (68 Tower) yang berpotensi terjadi N-4 SUTT (Rbkit-Pati 1,2 &amp; Rbkit-Rembang 12), karena berada pada Lokasi tanah yang labil. Secara histori sudah pernah terjadi N-4 SUTT outlet PLTU Rembang pada tanggal 25 Februari 2020 disebabkan tower roboh pada T.67, serta kegagalan struktur pada T.68 pada April 2024 sesuai surat MAN UPT Semarang Tanggal 28 April 2024 No.0732/TRS.01.03/F350 70000/2024</t>
+          <t>[BELUM_DITETAPKAN] 1. Outlet PLTU Rembang 2x280 MW terhubung dengan Subsistem Tanjung Jati melalui 2 sirkit radial SUTT 150 kV PLTU Rembang-Pati- Jekulo-Kudus dan PLTU Rembang-Sindo-Blora- Cepu. 2. Outlet PLTU Rembang terletak pada tower combined pada T.3-T.70 (68 Tower) yang berpotensi terjadi N-4 SUTT (Rbkit-Pati 1,2 &amp; Rbkit-Rembang 12), karena berada pada Lokasi tanah yang labil. Secara histori sudah pernah terjadi N-4 SUTT outlet PLTU Rembang pada tanggal 25 Februari 2020 disebabkan tower roboh pada T.67, serta kegagalan struktur pada T.68 pada April 2024 sesuai surat MAN UPT Semarang Tanggal 28 April 2024 No.0732/TRS.01.03/F350 70000/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4994,12 +5061,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] 1. Pembebanan Trafo GI 150 kV Kudus &gt;80%. 2. Keterbatasan penyulang 20 kV di GI 150 kV Jepara dan GI 150 kV Jekulo yang merupakan GI tetangga untuk mengambil beban GI 150 kV Kudus</t>
+          <t>[BELUM_DITETAPKAN] 1. Pembebanan Trafo GI 150 kV Kudus &gt;80%. 2. Keterbatasan penyulang 20 kV di GI 150 kV Jepara dan GI 150 kV Jekulo yang merupakan GI tetangga untuk mengambil beban GI 150 kV Kudus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5029,12 +5096,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Ekskursi Tegangan di GI 150 kV Cepu dan Blora hingga 126 kV apabila PLTU Rembang keluar 2 unit</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Ekskursi Tegangan di GI 150 kV Cepu dan Blora hingga 126 kV apabila PLTU Rembang keluar 2 unit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5064,12 +5131,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] Konfigurasi GI 150 kV Medari masih single phi (Sanggrahan-Medari- Kentungan)</t>
+          <t>[BELUM_DITETAPKAN] Konfigurasi GI 150 kV Medari masih single phi (Sanggrahan-Medari- Kentungan)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5239,12 +5306,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Ungaran-Bawen &gt;60% apabila terjadi kontingensi N-1-1 ada ruas TBROK- Bawen/Sayung-Bawen saat memasok sampai wilayah Jogjakarta (subsistem Pedan 3,4), sehingga N-1 tidak terpenuhi</t>
+          <t>[N-1-1] Pembebanan SUTT 150 kV Ungaran-Bawen &gt;60% apabila terjadi kontingensi N-1-1 ada ruas TBROK- Bawen/Sayung-Bawen saat memasok sampai wilayah Jogjakarta (subsistem Pedan 3,4), sehingga N-1 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
